--- a/artfynd/A 56080-2025 artfynd.xlsx
+++ b/artfynd/A 56080-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129750149</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129750133</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129750170</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56080-2025 artfynd.xlsx
+++ b/artfynd/A 56080-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129750149</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129750170</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56080-2025 artfynd.xlsx
+++ b/artfynd/A 56080-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129750149</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129750170</v>
       </c>
       <c r="B4" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56080-2025 artfynd.xlsx
+++ b/artfynd/A 56080-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129750149</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129750170</v>
       </c>
       <c r="B4" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56080-2025 artfynd.xlsx
+++ b/artfynd/A 56080-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129750149</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56080-2025 artfynd.xlsx
+++ b/artfynd/A 56080-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129750149</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129750133</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129750170</v>
       </c>
       <c r="B4" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56080-2025 artfynd.xlsx
+++ b/artfynd/A 56080-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129750149</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129750133</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129750170</v>
       </c>
       <c r="B4" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56080-2025 artfynd.xlsx
+++ b/artfynd/A 56080-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129750149</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129750170</v>
       </c>
       <c r="B4" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56080-2025 artfynd.xlsx
+++ b/artfynd/A 56080-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129750149</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129750133</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129750170</v>
       </c>
       <c r="B4" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56080-2025 artfynd.xlsx
+++ b/artfynd/A 56080-2025 artfynd.xlsx
@@ -675,57 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129750149</v>
+        <v>129750170</v>
       </c>
       <c r="B2" t="n">
-        <v>98830</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 56080, L Fårhult, Sm</t>
+          <t>A 56080, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583718</v>
+        <v>583786</v>
       </c>
       <c r="R2" t="n">
-        <v>6401158</v>
+        <v>6401128</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gamla</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +792,7 @@
         <v>129750133</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,56 +898,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129750170</v>
+        <v>129750149</v>
       </c>
       <c r="B4" t="n">
-        <v>92920</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 56080, Sm</t>
+          <t>A 56080, L Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583786</v>
+        <v>583718</v>
       </c>
       <c r="R4" t="n">
-        <v>6401128</v>
+        <v>6401158</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,11 +981,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gamla</t>
         </is>
       </c>
       <c r="AD4" t="b">
